--- a/shap_values.xlsx
+++ b/shap_values.xlsx
@@ -618,1222 +618,1222 @@
     </row>
     <row r="2" spans="1:40">
       <c r="A2">
-        <v>-0.009872638741667007</v>
+        <v>-0.001657073395303052</v>
       </c>
       <c r="B2">
-        <v>0.02137184562792811</v>
+        <v>0.01925806853206167</v>
       </c>
       <c r="C2">
-        <v>-0.004900236549677833</v>
+        <v>-0.003723352426705713</v>
       </c>
       <c r="D2">
-        <v>-5.163864989819438E-05</v>
+        <v>-7.295383858746054E-05</v>
       </c>
       <c r="E2">
-        <v>9.336020323421506E-05</v>
+        <v>-0.001384163984588104</v>
       </c>
       <c r="F2">
-        <v>-0.03840679079658977</v>
+        <v>-0.003650701006015493</v>
       </c>
       <c r="G2">
-        <v>0.00721881053447385</v>
+        <v>0.02191006389113881</v>
       </c>
       <c r="H2">
-        <v>-8.976872653242755E-05</v>
+        <v>-8.86393822319459E-05</v>
       </c>
       <c r="I2">
-        <v>0.001693895846981324</v>
+        <v>0.0006708637712301303</v>
       </c>
       <c r="J2">
-        <v>0.0007098479767702934</v>
+        <v>4.01579472276937E-05</v>
       </c>
       <c r="K2">
-        <v>0.005098849034828296</v>
+        <v>0.008426460724847208</v>
       </c>
       <c r="L2">
-        <v>0.02625501498224111</v>
+        <v>-0.02003496377075095</v>
       </c>
       <c r="M2">
-        <v>-0.002354138432133782</v>
+        <v>-0.001615309120859754</v>
       </c>
       <c r="N2">
-        <v>-0.000132186207185755</v>
+        <v>-0.0001431489313710118</v>
       </c>
       <c r="O2">
-        <v>-0.004604969971461394</v>
+        <v>-0.006164326936950317</v>
       </c>
       <c r="P2">
-        <v>-0.03656109190387381</v>
+        <v>0.03996354391628966</v>
       </c>
       <c r="Q2">
-        <v>0.005906610147281274</v>
+        <v>0.01025168869290325</v>
       </c>
       <c r="R2">
-        <v>-7.175242533128171E-05</v>
+        <v>-8.021093473929766E-05</v>
       </c>
       <c r="S2">
-        <v>0.003534730388641754</v>
+        <v>0.0002283058919260423</v>
       </c>
       <c r="T2">
-        <v>0.0002327024789558815</v>
+        <v>-0.0001210461877668612</v>
       </c>
       <c r="U2">
-        <v>-0.008459917733994189</v>
+        <v>-0.006510870040697542</v>
       </c>
       <c r="V2">
-        <v>0.02877988584565412</v>
+        <v>0.006418247792277493</v>
       </c>
       <c r="W2">
-        <v>-0.00619449962213589</v>
+        <v>-0.00557372653943907</v>
       </c>
       <c r="X2">
-        <v>-5.421034524915657E-05</v>
+        <v>-6.328195343377015E-05</v>
       </c>
       <c r="Y2">
-        <v>0.001316599334950885</v>
+        <v>-0.0005054763293382186</v>
       </c>
       <c r="Z2">
-        <v>-0.04528592797036708</v>
+        <v>-0.05716875220489921</v>
       </c>
       <c r="AA2">
-        <v>-0.007127596433705971</v>
+        <v>-0.002788511956387515</v>
       </c>
       <c r="AB2">
-        <v>-5.35910136617348E-05</v>
+        <v>-7.898690860117269E-05</v>
       </c>
       <c r="AC2">
-        <v>0.0002642776804484682</v>
+        <v>0.0002427888085007626</v>
       </c>
       <c r="AD2">
-        <v>-0.005102697938743713</v>
+        <v>0.002085879212637451</v>
       </c>
       <c r="AE2">
-        <v>-0.008259302636865253</v>
+        <v>-0.007661535557511815</v>
       </c>
       <c r="AF2">
-        <v>0.03209432451069923</v>
+        <v>0.04391745674322001</v>
       </c>
       <c r="AG2">
-        <v>-0.00694435386750987</v>
+        <v>-0.006641148631050216</v>
       </c>
       <c r="AH2">
-        <v>-9.50278238039126E-05</v>
+        <v>-7.898392878223385E-05</v>
       </c>
       <c r="AI2">
-        <v>-0.004614434077126555</v>
+        <v>-0.002389426799612145</v>
       </c>
       <c r="AJ2">
-        <v>0.01418270226729248</v>
+        <v>-0.02038383415433884</v>
       </c>
       <c r="AK2">
-        <v>0.01808287100342801</v>
+        <v>0.005271138098133996</v>
       </c>
       <c r="AL2">
-        <v>1.798524672656502E-05</v>
+        <v>-4.49991288213962E-05</v>
       </c>
       <c r="AM2">
-        <v>0.001709578072108079</v>
+        <v>0.003637068684943838</v>
       </c>
       <c r="AN2">
-        <v>0.001683342139885336</v>
+        <v>-0.002508251477610007</v>
       </c>
     </row>
     <row r="3" spans="1:40">
       <c r="A3">
-        <v>-1.098086434540877E-05</v>
+        <v>9.850481084298179E-05</v>
       </c>
       <c r="B3">
-        <v>0.000333622629727856</v>
+        <v>0.0004189864746501793</v>
       </c>
       <c r="C3">
-        <v>-0.0003945557697106543</v>
+        <v>0.000197245008567012</v>
       </c>
       <c r="D3">
-        <v>-7.134556987237546E-05</v>
+        <v>-6.802052592502612E-05</v>
       </c>
       <c r="E3">
-        <v>-0.007414101579761711</v>
+        <v>-0.004441587491494064</v>
       </c>
       <c r="F3">
-        <v>0.1457316949858416</v>
+        <v>0.081914813047804</v>
       </c>
       <c r="G3">
-        <v>-0.01594244446073724</v>
+        <v>-0.02413444356793479</v>
       </c>
       <c r="H3">
-        <v>-0.0001559488520897849</v>
+        <v>-0.0001641190037676131</v>
       </c>
       <c r="I3">
-        <v>0.0004237001717672479</v>
+        <v>0.0002703227405525472</v>
       </c>
       <c r="J3">
-        <v>0.0006093760820283957</v>
+        <v>0.000264212976052254</v>
       </c>
       <c r="K3">
-        <v>7.531121408631873E-05</v>
+        <v>0.0001426189664769374</v>
       </c>
       <c r="L3">
-        <v>0.0002443895779122469</v>
+        <v>0.000176254195341576</v>
       </c>
       <c r="M3">
-        <v>-0.001569318072440259</v>
+        <v>-0.00242026356489824</v>
       </c>
       <c r="N3">
-        <v>-4.940147057327158E-05</v>
+        <v>-2.535578910108882E-05</v>
       </c>
       <c r="O3">
-        <v>-0.006129853019218459</v>
+        <v>-0.004365830260236717</v>
       </c>
       <c r="P3">
-        <v>0.1295773579408677</v>
+        <v>0.1864500645227662</v>
       </c>
       <c r="Q3">
-        <v>0.00819367915538559</v>
+        <v>0.005128695310970492</v>
       </c>
       <c r="R3">
-        <v>-3.970251311958317E-05</v>
+        <v>-0.0001361266672949308</v>
       </c>
       <c r="S3">
-        <v>0.001820662008223124</v>
+        <v>0.003870303524966011</v>
       </c>
       <c r="T3">
-        <v>-0.0001236252059254181</v>
+        <v>0.0003712623088263058</v>
       </c>
       <c r="U3">
-        <v>-1.891405649288905E-05</v>
+        <v>-3.937379870784853E-05</v>
       </c>
       <c r="V3">
-        <v>0.0001664591374798479</v>
+        <v>9.716188858089764E-05</v>
       </c>
       <c r="W3">
-        <v>-0.003338423919778875</v>
+        <v>-0.002637317694557397</v>
       </c>
       <c r="X3">
-        <v>-7.092496541458767E-05</v>
+        <v>-4.559717592322772E-05</v>
       </c>
       <c r="Y3">
-        <v>-0.007331132811406363</v>
+        <v>-0.004703976396526483</v>
       </c>
       <c r="Z3">
-        <v>0.1329550499499776</v>
+        <v>0.1291103789593433</v>
       </c>
       <c r="AA3">
-        <v>0.007294988335123786</v>
+        <v>0.01023715752031147</v>
       </c>
       <c r="AB3">
-        <v>-0.0001521737389861425</v>
+        <v>-0.0001061254093802883</v>
       </c>
       <c r="AC3">
-        <v>0.004566622731449393</v>
+        <v>0.0004052791740515508</v>
       </c>
       <c r="AD3">
-        <v>-0.003388407937315594</v>
+        <v>0.002379467846005463</v>
       </c>
       <c r="AE3">
-        <v>5.223189262664383E-05</v>
+        <v>4.331604359223773E-05</v>
       </c>
       <c r="AF3">
-        <v>0.0003040574005055374</v>
+        <v>0.0004247575839567435</v>
       </c>
       <c r="AG3">
-        <v>-0.001490740922025199</v>
+        <v>-0.002512692667371245</v>
       </c>
       <c r="AH3">
-        <v>-5.283496092021247E-05</v>
+        <v>-1.358355316152166E-05</v>
       </c>
       <c r="AI3">
-        <v>-0.002833052212566815</v>
+        <v>-0.002923684698210657</v>
       </c>
       <c r="AJ3">
-        <v>0.07161302919715427</v>
+        <v>0.1158073605273991</v>
       </c>
       <c r="AK3">
-        <v>-0.009685625834762714</v>
+        <v>-0.007154502674811596</v>
       </c>
       <c r="AL3">
-        <v>-1.87416600509557E-05</v>
+        <v>-0.0001738761741050181</v>
       </c>
       <c r="AM3">
-        <v>0.002323249821440627</v>
+        <v>0.003675405415740848</v>
       </c>
       <c r="AN3">
-        <v>0.002720117859121287</v>
+        <v>0.0005043115982376913</v>
       </c>
     </row>
     <row r="4" spans="1:40">
       <c r="A4">
-        <v>-0.0001563410081489165</v>
+        <v>-6.041127526976042E-05</v>
       </c>
       <c r="B4">
-        <v>-0.0003160811685465484</v>
+        <v>-0.0003235833331767604</v>
       </c>
       <c r="C4">
-        <v>-0.6833946537855686</v>
+        <v>-0.6636172336425746</v>
       </c>
       <c r="D4">
-        <v>-0.01199268907697476</v>
+        <v>-0.01212240472420551</v>
       </c>
       <c r="E4">
-        <v>-0.8397090777836747</v>
+        <v>-0.7701150944620737</v>
       </c>
       <c r="F4">
-        <v>0.1100292379956634</v>
+        <v>0.1646263554444107</v>
       </c>
       <c r="G4">
-        <v>-0.005014257105207487</v>
+        <v>-0.007214176262399567</v>
       </c>
       <c r="H4">
-        <v>-0.0001159955075043417</v>
+        <v>-0.0001865646575581257</v>
       </c>
       <c r="I4">
-        <v>0.3319619440078252</v>
+        <v>0.342780009530206</v>
       </c>
       <c r="J4">
-        <v>-0.001681015542153129</v>
+        <v>-0.01033306981170652</v>
       </c>
       <c r="K4">
-        <v>-0.0001761388073596663</v>
+        <v>-0.0001242439074458386</v>
       </c>
       <c r="L4">
-        <v>-0.0002675855686547172</v>
+        <v>-0.0005689443520721314</v>
       </c>
       <c r="M4">
-        <v>-0.6923309798582084</v>
+        <v>-0.7204100734978113</v>
       </c>
       <c r="N4">
-        <v>-0.01226517851334564</v>
+        <v>-0.01280905094985201</v>
       </c>
       <c r="O4">
-        <v>-0.8155980668770563</v>
+        <v>-0.798763811005862</v>
       </c>
       <c r="P4">
-        <v>0.174800419889239</v>
+        <v>0.2165106880178335</v>
       </c>
       <c r="Q4">
-        <v>-0.009934500976590464</v>
+        <v>-0.008569157628373663</v>
       </c>
       <c r="R4">
-        <v>-0.0001455760859035809</v>
+        <v>-0.0001491078279210342</v>
       </c>
       <c r="S4">
-        <v>0.3303179416084991</v>
+        <v>0.3152140213676001</v>
       </c>
       <c r="T4">
-        <v>0.0003343583013578468</v>
+        <v>-0.0003970402698147176</v>
       </c>
       <c r="U4">
-        <v>-0.0002715610931674329</v>
+        <v>-0.0001755004936960274</v>
       </c>
       <c r="V4">
-        <v>-0.0007520382430533083</v>
+        <v>-0.001012997970746881</v>
       </c>
       <c r="W4">
-        <v>-0.7325873668972024</v>
+        <v>-0.752701482839497</v>
       </c>
       <c r="X4">
-        <v>-0.01255219392502056</v>
+        <v>-0.01242325505756889</v>
       </c>
       <c r="Y4">
-        <v>-0.7966690950978849</v>
+        <v>-0.8188255401363147</v>
       </c>
       <c r="Z4">
-        <v>0.1684828888272069</v>
+        <v>0.1477675130713336</v>
       </c>
       <c r="AA4">
-        <v>-0.004352450320380781</v>
+        <v>-0.006928473569486977</v>
       </c>
       <c r="AB4">
-        <v>-0.0001443659449839121</v>
+        <v>-0.00015273833552504</v>
       </c>
       <c r="AC4">
-        <v>0.3562237564675366</v>
+        <v>0.3512045846138717</v>
       </c>
       <c r="AD4">
-        <v>0.002518650647274196</v>
+        <v>0.0009359444452123602</v>
       </c>
       <c r="AE4">
-        <v>-0.0001486098296451978</v>
+        <v>-0.0001511248629468188</v>
       </c>
       <c r="AF4">
-        <v>-0.0002143240779199806</v>
+        <v>-0.0005181393135330462</v>
       </c>
       <c r="AG4">
-        <v>-0.6554446492101557</v>
+        <v>-0.6479163506179557</v>
       </c>
       <c r="AH4">
-        <v>-0.01248393057093295</v>
+        <v>-0.01265846643440374</v>
       </c>
       <c r="AI4">
-        <v>-0.7873238993773813</v>
+        <v>-0.7788091214257267</v>
       </c>
       <c r="AJ4">
-        <v>0.1086425746113512</v>
+        <v>0.1518418667452854</v>
       </c>
       <c r="AK4">
-        <v>-0.006500569196351598</v>
+        <v>-0.005319170273958735</v>
       </c>
       <c r="AL4">
-        <v>-1.835863869599524E-05</v>
+        <v>-0.0001132603625669737</v>
       </c>
       <c r="AM4">
-        <v>0.3655479158098958</v>
+        <v>0.3608325999013084</v>
       </c>
       <c r="AN4">
-        <v>-0.002720913606907316</v>
+        <v>-0.0005261789450900848</v>
       </c>
     </row>
     <row r="5" spans="1:40">
       <c r="A5">
-        <v>-1.975110559179731E-05</v>
+        <v>4.114918697535232E-05</v>
       </c>
       <c r="B5">
-        <v>0.0003874403403759173</v>
+        <v>0.0004434796881806397</v>
       </c>
       <c r="C5">
-        <v>-0.6562744375845655</v>
+        <v>-0.6307020385132258</v>
       </c>
       <c r="D5">
-        <v>-0.01011140451587568</v>
+        <v>-0.01030263491497089</v>
       </c>
       <c r="E5">
-        <v>-0.7158768845115079</v>
+        <v>-0.7203467258511381</v>
       </c>
       <c r="F5">
-        <v>0.1344775708737138</v>
+        <v>0.133270190210653</v>
       </c>
       <c r="G5">
-        <v>-0.008786598073604305</v>
+        <v>-0.0058690260590636</v>
       </c>
       <c r="H5">
-        <v>-0.00014655502465337</v>
+        <v>-0.0001137378698008455</v>
       </c>
       <c r="I5">
-        <v>0.3439880570345148</v>
+        <v>0.3413927092081847</v>
       </c>
       <c r="J5">
-        <v>-0.001072439610452935</v>
+        <v>-0.01029892971337268</v>
       </c>
       <c r="K5">
-        <v>7.336656232917276E-05</v>
+        <v>0.0001554048370706189</v>
       </c>
       <c r="L5">
-        <v>0.0004709831771342343</v>
+        <v>5.936746856742472E-05</v>
       </c>
       <c r="M5">
-        <v>-0.6999110623505885</v>
+        <v>-0.6824782075619612</v>
       </c>
       <c r="N5">
-        <v>-0.01063823107115282</v>
+        <v>-0.01083648986832406</v>
       </c>
       <c r="O5">
-        <v>-0.7263057748078726</v>
+        <v>-0.7173475231580037</v>
       </c>
       <c r="P5">
-        <v>0.1499697391060418</v>
+        <v>0.1448909234712218</v>
       </c>
       <c r="Q5">
-        <v>-0.007475189701269138</v>
+        <v>-0.008474077369300252</v>
       </c>
       <c r="R5">
-        <v>-0.0001283179371817658</v>
+        <v>-0.0001195694659755632</v>
       </c>
       <c r="S5">
-        <v>0.3433016055096149</v>
+        <v>0.3373597310682142</v>
       </c>
       <c r="T5">
-        <v>-0.0009814077360386045</v>
+        <v>7.080784404849039E-05</v>
       </c>
       <c r="U5">
-        <v>-0.0001022228134578808</v>
+        <v>-6.404180460947721E-05</v>
       </c>
       <c r="V5">
-        <v>-0.0001004848483080999</v>
+        <v>-0.0002274000600949649</v>
       </c>
       <c r="W5">
-        <v>-0.7261567168201829</v>
+        <v>-0.7288993246055221</v>
       </c>
       <c r="X5">
-        <v>-0.0109461256436304</v>
+        <v>-0.01055018893977797</v>
       </c>
       <c r="Y5">
-        <v>-0.7591231180005525</v>
+        <v>-0.7559465330768376</v>
       </c>
       <c r="Z5">
-        <v>0.1691603292934692</v>
+        <v>0.1587739882390457</v>
       </c>
       <c r="AA5">
-        <v>-0.008759372383324847</v>
+        <v>-0.007768452751237882</v>
       </c>
       <c r="AB5">
-        <v>-0.000182896783076895</v>
+        <v>-0.0001321994771136114</v>
       </c>
       <c r="AC5">
-        <v>0.3534961861993193</v>
+        <v>0.3558240847087562</v>
       </c>
       <c r="AD5">
-        <v>0.003323864300761828</v>
+        <v>-0.0005983195142332363</v>
       </c>
       <c r="AE5">
-        <v>1.73978218501799E-05</v>
+        <v>3.039292760231682E-05</v>
       </c>
       <c r="AF5">
-        <v>0.0005003949099047539</v>
+        <v>0.0004416685517889633</v>
       </c>
       <c r="AG5">
-        <v>-0.6110263867171102</v>
+        <v>-0.584451348917491</v>
       </c>
       <c r="AH5">
-        <v>-0.01063911152557079</v>
+        <v>-0.01068030381963489</v>
       </c>
       <c r="AI5">
-        <v>-0.724677262588422</v>
+        <v>-0.6978086954233755</v>
       </c>
       <c r="AJ5">
-        <v>0.1291911195031569</v>
+        <v>0.1145809916786561</v>
       </c>
       <c r="AK5">
-        <v>-0.01142531792822184</v>
+        <v>-0.007603330673097694</v>
       </c>
       <c r="AL5">
-        <v>-6.764281621936847E-05</v>
+        <v>-0.000139181490793479</v>
       </c>
       <c r="AM5">
-        <v>0.3497598297409025</v>
+        <v>0.3489224424254915</v>
       </c>
       <c r="AN5">
-        <v>-0.003273889886296713</v>
+        <v>-0.0002337035219977869</v>
       </c>
     </row>
     <row r="6" spans="1:40">
       <c r="A6">
-        <v>-3.429541156903357E-05</v>
+        <v>-2.547967728894637E-05</v>
       </c>
       <c r="B6">
-        <v>-0.0002596003147531918</v>
+        <v>-0.0005757052370258243</v>
       </c>
       <c r="C6">
-        <v>-0.01182771668774572</v>
+        <v>-0.003396754723067994</v>
       </c>
       <c r="D6">
-        <v>0.0001930788717160614</v>
+        <v>-6.76802067089909E-05</v>
       </c>
       <c r="E6">
-        <v>-0.006512166045620204</v>
+        <v>-0.005307898966839497</v>
       </c>
       <c r="F6">
-        <v>0.2040809846914791</v>
+        <v>0.1367489044746557</v>
       </c>
       <c r="G6">
-        <v>-0.009961274394595637</v>
+        <v>-0.008531273883490993</v>
       </c>
       <c r="H6">
-        <v>-6.850216083094641E-05</v>
+        <v>-6.666853338349164E-05</v>
       </c>
       <c r="I6">
-        <v>0.3589445902909281</v>
+        <v>0.3496159276739779</v>
       </c>
       <c r="J6">
-        <v>-0.002394785846787932</v>
+        <v>-0.01154872936669543</v>
       </c>
       <c r="K6">
-        <v>-5.92238074597695E-05</v>
+        <v>-3.215312437688528E-05</v>
       </c>
       <c r="L6">
-        <v>-0.0002475991695780342</v>
+        <v>-0.0002457091755759569</v>
       </c>
       <c r="M6">
-        <v>0.000788055493268321</v>
+        <v>-0.002010932264536291</v>
       </c>
       <c r="N6">
-        <v>-0.0001145030757377695</v>
+        <v>-1.061928976480368E-05</v>
       </c>
       <c r="O6">
-        <v>0.001725630097952614</v>
+        <v>-0.003540985930475344</v>
       </c>
       <c r="P6">
-        <v>0.2004212839847734</v>
+        <v>0.2533615793117994</v>
       </c>
       <c r="Q6">
-        <v>-0.008266565019070504</v>
+        <v>-0.007365907783485982</v>
       </c>
       <c r="R6">
-        <v>-8.340709214770556E-05</v>
+        <v>-0.0001080952280306408</v>
       </c>
       <c r="S6">
-        <v>0.3565129640381795</v>
+        <v>0.3638904915354797</v>
       </c>
       <c r="T6">
-        <v>-0.0007976993535801015</v>
+        <v>-0.0005853351721331529</v>
       </c>
       <c r="U6">
-        <v>-5.482190678424126E-05</v>
+        <v>-0.0001089340038521992</v>
       </c>
       <c r="V6">
-        <v>-0.0003184619418883747</v>
+        <v>-0.0001852664059026562</v>
       </c>
       <c r="W6">
-        <v>-0.007151318003392853</v>
+        <v>-0.003469264057023783</v>
       </c>
       <c r="X6">
-        <v>6.589046119004329E-05</v>
+        <v>-0.0001438774749870136</v>
       </c>
       <c r="Y6">
-        <v>0.002095172177774056</v>
+        <v>-0.006319903994812674</v>
       </c>
       <c r="Z6">
-        <v>0.203267504362771</v>
+        <v>0.2443197148792121</v>
       </c>
       <c r="AA6">
-        <v>-0.008166793713086028</v>
+        <v>-0.01000179419845798</v>
       </c>
       <c r="AB6">
-        <v>-0.0001216702009469795</v>
+        <v>-9.892264496164804E-05</v>
       </c>
       <c r="AC6">
-        <v>0.3652220673651879</v>
+        <v>0.3813105031935759</v>
       </c>
       <c r="AD6">
-        <v>0.004195949700767376</v>
+        <v>-0.0002308173559562201</v>
       </c>
       <c r="AE6">
-        <v>-6.631288330889017E-05</v>
+        <v>-9.555054548716775E-06</v>
       </c>
       <c r="AF6">
-        <v>-0.0003971913230804102</v>
+        <v>-0.0001143411190654595</v>
       </c>
       <c r="AG6">
-        <v>-0.01221484591533442</v>
+        <v>-0.01196600749990468</v>
       </c>
       <c r="AH6">
-        <v>-0.0001955347564626619</v>
+        <v>-0.0002145447165600746</v>
       </c>
       <c r="AI6">
-        <v>-0.002467260372636559</v>
+        <v>0.009150264260478944</v>
       </c>
       <c r="AJ6">
-        <v>0.1505662387833469</v>
+        <v>0.1933762509156481</v>
       </c>
       <c r="AK6">
-        <v>-0.009486621070195657</v>
+        <v>-0.007298152572757614</v>
       </c>
       <c r="AL6">
-        <v>-2.894581189987593E-05</v>
+        <v>-5.831251667508052E-05</v>
       </c>
       <c r="AM6">
-        <v>0.3686302522804434</v>
+        <v>0.373781330237446</v>
       </c>
       <c r="AN6">
-        <v>-0.002906039581955847</v>
+        <v>-0.001060652860762208</v>
       </c>
     </row>
     <row r="7" spans="1:40">
       <c r="A7">
-        <v>-0.0002698788369335252</v>
+        <v>-0.0002005779964476075</v>
       </c>
       <c r="B7">
-        <v>-0.0007675091635875818</v>
+        <v>-0.0001882455452026942</v>
       </c>
       <c r="C7">
-        <v>-0.002581600068445448</v>
+        <v>-0.001509550251186805</v>
       </c>
       <c r="D7">
-        <v>-1.378741961571796E-06</v>
+        <v>-7.017406938996911E-06</v>
       </c>
       <c r="E7">
-        <v>-0.0009888720536246967</v>
+        <v>0.0002240424995100928</v>
       </c>
       <c r="F7">
-        <v>1.048931389920969</v>
+        <v>1.337473301662976</v>
       </c>
       <c r="G7">
-        <v>-0.05172499425630989</v>
+        <v>-0.06142625050219985</v>
       </c>
       <c r="H7">
-        <v>-5.487430837639461E-05</v>
+        <v>-0.0001536447505167991</v>
       </c>
       <c r="I7">
-        <v>0.002077410399508366</v>
+        <v>7.59633618700768E-05</v>
       </c>
       <c r="J7">
-        <v>-0.001492382653559654</v>
+        <v>-0.001411811565951582</v>
       </c>
       <c r="K7">
-        <v>-0.0002249438129750032</v>
+        <v>9.957071975078231E-05</v>
       </c>
       <c r="L7">
-        <v>-0.001866600188914189</v>
+        <v>0.0007233459488223262</v>
       </c>
       <c r="M7">
-        <v>0.0009328018890323711</v>
+        <v>-0.003200108227340567</v>
       </c>
       <c r="N7">
-        <v>-2.263423312253239E-05</v>
+        <v>3.230713832927541E-05</v>
       </c>
       <c r="O7">
-        <v>0.0004106587782507559</v>
+        <v>0.002635044546196695</v>
       </c>
       <c r="P7">
-        <v>1.603486338176056</v>
+        <v>1.653891044691514</v>
       </c>
       <c r="Q7">
-        <v>-0.06671453391311193</v>
+        <v>-0.05988554536783659</v>
       </c>
       <c r="R7">
-        <v>-8.472990410236527E-05</v>
+        <v>-6.520705641154121E-05</v>
       </c>
       <c r="S7">
-        <v>0.005205687480458676</v>
+        <v>0.002948372639676466</v>
       </c>
       <c r="T7">
-        <v>-0.006142465352174178</v>
+        <v>-0.01932902357989192</v>
       </c>
       <c r="U7">
-        <v>-0.0001713435821429516</v>
+        <v>-0.0001905884666511617</v>
       </c>
       <c r="V7">
-        <v>0.0006367369919941674</v>
+        <v>-0.0007567323668717108</v>
       </c>
       <c r="W7">
-        <v>-0.001175827606687359</v>
+        <v>0.0008373926397742173</v>
       </c>
       <c r="X7">
-        <v>3.295580596499756E-05</v>
+        <v>2.947870990218804E-05</v>
       </c>
       <c r="Y7">
-        <v>0.0003162553536267432</v>
+        <v>0.004804177168046575</v>
       </c>
       <c r="Z7">
-        <v>2.00065059941073</v>
+        <v>1.643240385520591</v>
       </c>
       <c r="AA7">
-        <v>-0.04271207713968447</v>
+        <v>-0.03535497906641207</v>
       </c>
       <c r="AB7">
-        <v>-1.993676304396296E-05</v>
+        <v>1.504011810362531E-05</v>
       </c>
       <c r="AC7">
-        <v>0.0009278013628502283</v>
+        <v>0.007103480951845285</v>
       </c>
       <c r="AD7">
-        <v>-0.002931690761425999</v>
+        <v>0.00388469309867992</v>
       </c>
       <c r="AE7">
-        <v>-9.575729640402516E-05</v>
+        <v>-5.453711200607817E-05</v>
       </c>
       <c r="AF7">
-        <v>0.0003625504550709842</v>
+        <v>0.0001560224013020914</v>
       </c>
       <c r="AG7">
-        <v>0.0006857453625919185</v>
+        <v>-0.00445758678491177</v>
       </c>
       <c r="AH7">
-        <v>-1.361066333001877E-05</v>
+        <v>8.695300821579573E-07</v>
       </c>
       <c r="AI7">
-        <v>-0.0005832980336027664</v>
+        <v>-0.001760530833981166</v>
       </c>
       <c r="AJ7">
-        <v>1.895061537909328</v>
+        <v>1.684546021522277</v>
       </c>
       <c r="AK7">
-        <v>-0.03567630518241202</v>
+        <v>-0.008014900686282911</v>
       </c>
       <c r="AL7">
-        <v>3.243897872267656E-05</v>
+        <v>7.422387653748315E-06</v>
       </c>
       <c r="AM7">
-        <v>0.0004240351593649263</v>
+        <v>-0.0003000921419368105</v>
       </c>
       <c r="AN7">
-        <v>0.009816602945911919</v>
+        <v>-0.002180396022746973</v>
       </c>
     </row>
     <row r="8" spans="1:40">
       <c r="A8">
-        <v>-0.0001619131917959179</v>
+        <v>-0.0001897683198845674</v>
       </c>
       <c r="B8">
-        <v>-0.0004399466981141957</v>
+        <v>4.262805572832336E-05</v>
       </c>
       <c r="C8">
-        <v>-0.0004740829030490314</v>
+        <v>-0.00230976139921913</v>
       </c>
       <c r="D8">
-        <v>6.316834263626364E-05</v>
+        <v>1.592113374122116E-05</v>
       </c>
       <c r="E8">
-        <v>0.008022613711379694</v>
+        <v>0.004931698700851825</v>
       </c>
       <c r="F8">
-        <v>0.4816679518712886</v>
+        <v>0.2828488143212517</v>
       </c>
       <c r="G8">
-        <v>0.00583261234261133</v>
+        <v>0.008680304359171906</v>
       </c>
       <c r="H8">
-        <v>-4.78731463365518E-05</v>
+        <v>-0.0001676085432916599</v>
       </c>
       <c r="I8">
-        <v>-0.002024268589390003</v>
+        <v>0.0009290569980506671</v>
       </c>
       <c r="J8">
-        <v>-0.001390002316774845</v>
+        <v>-8.097886484492782E-05</v>
       </c>
       <c r="K8">
-        <v>3.872588426251212E-05</v>
+        <v>-0.0001528376369862532</v>
       </c>
       <c r="L8">
-        <v>0.0004723222796197922</v>
+        <v>-0.000268614926805518</v>
       </c>
       <c r="M8">
-        <v>-0.0001960705903192659</v>
+        <v>-0.002231289712856627</v>
       </c>
       <c r="N8">
-        <v>2.9718956907926E-05</v>
+        <v>6.50331758060111E-06</v>
       </c>
       <c r="O8">
-        <v>0.004402453904469629</v>
+        <v>0.00368186871455096</v>
       </c>
       <c r="P8">
-        <v>0.2868762442878034</v>
+        <v>-0.006656327784255174</v>
       </c>
       <c r="Q8">
-        <v>0.013218037213468</v>
+        <v>0.007302184663985915</v>
       </c>
       <c r="R8">
-        <v>-0.0001093707464966615</v>
+        <v>-0.00016601859092944</v>
       </c>
       <c r="S8">
-        <v>0.0005192371123332933</v>
+        <v>-0.0006886573096029578</v>
       </c>
       <c r="T8">
-        <v>-0.000150664338506151</v>
+        <v>0.01200238636286866</v>
       </c>
       <c r="U8">
-        <v>-0.0003147899331333354</v>
+        <v>5.84882970470574E-06</v>
       </c>
       <c r="V8">
-        <v>-2.777634870568865E-05</v>
+        <v>-0.0005782540581745209</v>
       </c>
       <c r="W8">
-        <v>0.00733035358121796</v>
+        <v>0.0005215032623160236</v>
       </c>
       <c r="X8">
-        <v>7.010918881855445E-06</v>
+        <v>1.523305881548426E-05</v>
       </c>
       <c r="Y8">
-        <v>0.004194163026005639</v>
+        <v>0.008460915358045383</v>
       </c>
       <c r="Z8">
-        <v>0.2772040182683383</v>
+        <v>0.1165629944461691</v>
       </c>
       <c r="AA8">
-        <v>0.009610969930992093</v>
+        <v>0.009958948556589815</v>
       </c>
       <c r="AB8">
-        <v>-3.697163551344642E-05</v>
+        <v>-0.0001696970279056253</v>
       </c>
       <c r="AC8">
-        <v>-8.230575136948454E-05</v>
+        <v>-0.000778407343800557</v>
       </c>
       <c r="AD8">
-        <v>0.003032399168396851</v>
+        <v>-0.003032078940190389</v>
       </c>
       <c r="AE8">
-        <v>-6.55577874867383E-07</v>
+        <v>-0.000262538474746411</v>
       </c>
       <c r="AF8">
-        <v>0.0001089901496643134</v>
+        <v>-4.83121070377567E-06</v>
       </c>
       <c r="AG8">
-        <v>-0.001985859972943922</v>
+        <v>-0.001463981401541367</v>
       </c>
       <c r="AH8">
-        <v>-7.954393009229642E-06</v>
+        <v>-4.265729208526685E-06</v>
       </c>
       <c r="AI8">
-        <v>0.00196349370397758</v>
+        <v>0.003116260046048765</v>
       </c>
       <c r="AJ8">
-        <v>0.6841511649645722</v>
+        <v>0.8884101865310344</v>
       </c>
       <c r="AK8">
-        <v>0.004821625649692276</v>
+        <v>0.00849809916037522</v>
       </c>
       <c r="AL8">
-        <v>1.117654700257844E-05</v>
+        <v>-0.0001492537176996554</v>
       </c>
       <c r="AM8">
-        <v>-0.001914041235671345</v>
+        <v>-0.002477585281780142</v>
       </c>
       <c r="AN8">
-        <v>-0.0001390885313847886</v>
+        <v>0.0001944356728473176</v>
       </c>
     </row>
     <row r="9" spans="1:40">
       <c r="A9">
-        <v>-0.0001079797253721887</v>
+        <v>5.468919535405877E-05</v>
       </c>
       <c r="B9">
-        <v>0.000471707576440457</v>
+        <v>0.0001270801036267491</v>
       </c>
       <c r="C9">
-        <v>-0.4125022605319549</v>
+        <v>-0.3223259843448025</v>
       </c>
       <c r="D9">
-        <v>-0.006816508274777869</v>
+        <v>-0.006884362912959834</v>
       </c>
       <c r="E9">
-        <v>-0.463507823345601</v>
+        <v>-0.491188351906618</v>
       </c>
       <c r="F9">
-        <v>0.1005478734254038</v>
+        <v>0.1567806039680701</v>
       </c>
       <c r="G9">
-        <v>-0.004149438727002339</v>
+        <v>-0.002825665147109004</v>
       </c>
       <c r="H9">
-        <v>-8.559258814788661E-05</v>
+        <v>-5.166619570639582E-05</v>
       </c>
       <c r="I9">
-        <v>-0.002566693537407822</v>
+        <v>-0.001494060107364128</v>
       </c>
       <c r="J9">
-        <v>-0.01084663694927758</v>
+        <v>0.001584463068142062</v>
       </c>
       <c r="K9">
-        <v>5.651412823558595E-06</v>
+        <v>-1.742123105955574E-05</v>
       </c>
       <c r="L9">
-        <v>0.0006425244344989287</v>
+        <v>0.0001363640766203607</v>
       </c>
       <c r="M9">
-        <v>-0.2908875491953826</v>
+        <v>-0.255691811009183</v>
       </c>
       <c r="N9">
-        <v>-0.007945685344868994</v>
+        <v>-0.007745148375388317</v>
       </c>
       <c r="O9">
-        <v>-0.3450373634576457</v>
+        <v>-0.5322736536719318</v>
       </c>
       <c r="P9">
-        <v>0.103259476230967</v>
+        <v>0.1212567446497641</v>
       </c>
       <c r="Q9">
-        <v>-0.003341379010396096</v>
+        <v>-0.003149392481807142</v>
       </c>
       <c r="R9">
-        <v>-9.369746665562207E-05</v>
+        <v>-7.123561822736206E-05</v>
       </c>
       <c r="S9">
-        <v>0.0006209222219352869</v>
+        <v>0.0006571224630393064</v>
       </c>
       <c r="T9">
-        <v>0.002273791115753022</v>
+        <v>0.006838145228747951</v>
       </c>
       <c r="U9">
-        <v>5.606449193328449E-05</v>
+        <v>7.462096934116845E-05</v>
       </c>
       <c r="V9">
-        <v>0.0008545828438360709</v>
+        <v>0.000177555640552901</v>
       </c>
       <c r="W9">
-        <v>-0.3881067472503388</v>
+        <v>-0.3211026847644734</v>
       </c>
       <c r="X9">
-        <v>-0.00648740033026747</v>
+        <v>-0.005480204703497107</v>
       </c>
       <c r="Y9">
-        <v>-0.3962432334303558</v>
+        <v>-0.3535937802246929</v>
       </c>
       <c r="Z9">
-        <v>0.1162390467987249</v>
+        <v>0.1297486346648959</v>
       </c>
       <c r="AA9">
-        <v>-0.004030005676032615</v>
+        <v>-0.005069767868390929</v>
       </c>
       <c r="AB9">
-        <v>-0.0001050272948698791</v>
+        <v>-8.402507927334776E-05</v>
       </c>
       <c r="AC9">
-        <v>-0.001206601940654949</v>
+        <v>-0.002915557492601056</v>
       </c>
       <c r="AD9">
-        <v>0.0009677841123638152</v>
+        <v>0.003420997571497</v>
       </c>
       <c r="AE9">
-        <v>-8.607088343820281E-05</v>
+        <v>-5.872266091641837E-05</v>
       </c>
       <c r="AF9">
-        <v>0.0005553287533004296</v>
+        <v>0.0002844427906678146</v>
       </c>
       <c r="AG9">
-        <v>-0.4943751719148473</v>
+        <v>-0.2614946096900773</v>
       </c>
       <c r="AH9">
-        <v>-0.007591398154734479</v>
+        <v>-0.005616296989304572</v>
       </c>
       <c r="AI9">
-        <v>-0.3823900336094564</v>
+        <v>-0.4497416533675685</v>
       </c>
       <c r="AJ9">
-        <v>0.1551479702521028</v>
+        <v>0.1578180897369626</v>
       </c>
       <c r="AK9">
-        <v>-0.006665944678373985</v>
+        <v>-0.003939839264528366</v>
       </c>
       <c r="AL9">
-        <v>-2.861182385943785E-05</v>
+        <v>-5.299003187129446E-05</v>
       </c>
       <c r="AM9">
-        <v>-2.090320488466486E-05</v>
+        <v>0.0005731675515030311</v>
       </c>
       <c r="AN9">
-        <v>-0.005263449734341979</v>
+        <v>-0.008932453752449956</v>
       </c>
     </row>
     <row r="10" spans="1:40">
       <c r="A10">
-        <v>-7.083156616024876E-05</v>
+        <v>-0.0001152659657691559</v>
       </c>
       <c r="B10">
-        <v>-0.0003071177048044459</v>
+        <v>-0.0005210722172302802</v>
       </c>
       <c r="C10">
-        <v>-0.01329776276725377</v>
+        <v>-0.07226193656195404</v>
       </c>
       <c r="D10">
-        <v>-0.0003193001396163538</v>
+        <v>-0.001251884484564656</v>
       </c>
       <c r="E10">
-        <v>-0.02203051779117536</v>
+        <v>-0.09372481280117063</v>
       </c>
       <c r="F10">
-        <v>-0.09484974338182012</v>
+        <v>0.2835600199031136</v>
       </c>
       <c r="G10">
-        <v>0.004439933655546441</v>
+        <v>-0.01532753305934565</v>
       </c>
       <c r="H10">
-        <v>-0.0003813214656464116</v>
+        <v>-4.049420921060573E-05</v>
       </c>
       <c r="I10">
-        <v>0.01403741201015067</v>
+        <v>0.0505137597271347</v>
       </c>
       <c r="J10">
-        <v>-0.001270681751798224</v>
+        <v>-0.008783643598483673</v>
       </c>
       <c r="K10">
-        <v>4.885503163389358E-05</v>
+        <v>-0.0001091275442164053</v>
       </c>
       <c r="L10">
-        <v>8.822129680333879E-05</v>
+        <v>-0.0005114676007525785</v>
       </c>
       <c r="M10">
-        <v>-0.01362832635029907</v>
+        <v>-0.01397464252305969</v>
       </c>
       <c r="N10">
-        <v>-0.0003538754133432629</v>
+        <v>-0.0001926556133762812</v>
       </c>
       <c r="O10">
-        <v>-0.02265869664461717</v>
+        <v>-0.005007236204336281</v>
       </c>
       <c r="P10">
-        <v>-0.3967120385063543</v>
+        <v>0.3770144887891234</v>
       </c>
       <c r="Q10">
-        <v>0.004252661111021615</v>
+        <v>0.01796240846624949</v>
       </c>
       <c r="R10">
-        <v>-5.647817352849333E-05</v>
+        <v>-0.0002862225262970621</v>
       </c>
       <c r="S10">
-        <v>0.009462533857573075</v>
+        <v>0.006300682797919708</v>
       </c>
       <c r="T10">
-        <v>-0.0008506783028252961</v>
+        <v>-0.0001678015829301691</v>
       </c>
       <c r="U10">
-        <v>-0.0001659251758096824</v>
+        <v>0.0001973917557425207</v>
       </c>
       <c r="V10">
-        <v>-0.0009796638275679757</v>
+        <v>0.0009553955982742529</v>
       </c>
       <c r="W10">
-        <v>-0.01266656049882556</v>
+        <v>-0.0157796944607459</v>
       </c>
       <c r="X10">
-        <v>-0.0002312296429384212</v>
+        <v>-0.0001918364062830191</v>
       </c>
       <c r="Y10">
-        <v>-0.01274312833362142</v>
+        <v>-0.02033810767079453</v>
       </c>
       <c r="Z10">
-        <v>-0.2658383943412311</v>
+        <v>0.3774186234522582</v>
       </c>
       <c r="AA10">
-        <v>-0.02797001438503209</v>
+        <v>-0.02163709218305007</v>
       </c>
       <c r="AB10">
-        <v>-0.0002044034769949013</v>
+        <v>-0.000171282804197946</v>
       </c>
       <c r="AC10">
-        <v>0.009784924272653569</v>
+        <v>0.01246547024287623</v>
       </c>
       <c r="AD10">
-        <v>0.002478646585323877</v>
+        <v>-0.0001517553321407877</v>
       </c>
       <c r="AE10">
-        <v>0.0001191026814710664</v>
+        <v>0.0008016893381640487</v>
       </c>
       <c r="AF10">
-        <v>0.0002028110004893154</v>
+        <v>0.002974699328825387</v>
       </c>
       <c r="AG10">
-        <v>-0.009744004528495847</v>
+        <v>-0.01215244601771998</v>
       </c>
       <c r="AH10">
-        <v>-0.0001356205538292362</v>
+        <v>-0.0001826953619525395</v>
       </c>
       <c r="AI10">
-        <v>-0.009932581724186372</v>
+        <v>-0.01165953599996536</v>
       </c>
       <c r="AJ10">
-        <v>0.05688186436926081</v>
+        <v>-0.02337067957180348</v>
       </c>
       <c r="AK10">
-        <v>0.03472813080673653</v>
+        <v>0.003638857871354117</v>
       </c>
       <c r="AL10">
-        <v>-0.002423843909807673</v>
+        <v>-0.0004072445571875536</v>
       </c>
       <c r="AM10">
-        <v>0.007027758668387707</v>
+        <v>0.006039668210321972</v>
       </c>
       <c r="AN10">
-        <v>-0.00187375689580235</v>
+        <v>0.0002884171049650842</v>
       </c>
     </row>
     <row r="11" spans="1:40">
       <c r="A11">
-        <v>-0.0001590812597973352</v>
+        <v>-6.625437767592689E-05</v>
       </c>
       <c r="B11">
-        <v>0.0002799632436660238</v>
+        <v>0.0003053216647260152</v>
       </c>
       <c r="C11">
-        <v>-0.701204504700507</v>
+        <v>-0.697375806903561</v>
       </c>
       <c r="D11">
-        <v>-0.01268622121511282</v>
+        <v>-0.01263615586773263</v>
       </c>
       <c r="E11">
-        <v>-0.7889515405500171</v>
+        <v>-0.7652767427035472</v>
       </c>
       <c r="F11">
-        <v>0.1382409170090817</v>
+        <v>0.1637840005574152</v>
       </c>
       <c r="G11">
-        <v>-0.01461876525352598</v>
+        <v>-0.01231305052561692</v>
       </c>
       <c r="H11">
-        <v>-0.0001112703832565086</v>
+        <v>-0.0001673686210291772</v>
       </c>
       <c r="I11">
-        <v>0.5214198679300699</v>
+        <v>0.5159196240146158</v>
       </c>
       <c r="J11">
-        <v>-0.003677398346723053</v>
+        <v>-0.01221434268959033</v>
       </c>
       <c r="K11">
-        <v>5.860128582039614E-05</v>
+        <v>7.435871878901639E-05</v>
       </c>
       <c r="L11">
-        <v>-0.0001776339532118196</v>
+        <v>-0.0005362251145782511</v>
       </c>
       <c r="M11">
-        <v>-0.6754061741778088</v>
+        <v>-0.6736546183524553</v>
       </c>
       <c r="N11">
-        <v>-0.01228657980640208</v>
+        <v>-0.01221453753941384</v>
       </c>
       <c r="O11">
-        <v>-0.7737316128162272</v>
+        <v>-0.7778259104040459</v>
       </c>
       <c r="P11">
-        <v>0.08656214545210623</v>
+        <v>0.246691184792916</v>
       </c>
       <c r="Q11">
-        <v>-0.009796125721117988</v>
+        <v>-0.0100889206157225</v>
       </c>
       <c r="R11">
-        <v>-0.0002261052977103825</v>
+        <v>-0.0001675927125593261</v>
       </c>
       <c r="S11">
-        <v>0.5621112640127617</v>
+        <v>0.5589135702105382</v>
       </c>
       <c r="T11">
-        <v>-0.001311794207357088</v>
+        <v>0.0004330777174147688</v>
       </c>
       <c r="U11">
-        <v>4.89289731621926E-05</v>
+        <v>9.614341405870413E-05</v>
       </c>
       <c r="V11">
-        <v>0.0009227682699039203</v>
+        <v>0.0005197058600791052</v>
       </c>
       <c r="W11">
-        <v>-0.7173857313656092</v>
+        <v>-0.7168674009952113</v>
       </c>
       <c r="X11">
-        <v>-0.01283641106475557</v>
+        <v>-0.01278941196145322</v>
       </c>
       <c r="Y11">
-        <v>-0.7594114544550902</v>
+        <v>-0.7581939014802028</v>
       </c>
       <c r="Z11">
-        <v>0.1736388980964395</v>
+        <v>0.2865995492638112</v>
       </c>
       <c r="AA11">
-        <v>-0.009000084451092122</v>
+        <v>-0.006546621274893787</v>
       </c>
       <c r="AB11">
-        <v>-0.000144629866114718</v>
+        <v>-0.0001840509314619938</v>
       </c>
       <c r="AC11">
-        <v>0.5212266173020688</v>
+        <v>0.5212128686769176</v>
       </c>
       <c r="AD11">
-        <v>0.00211465412239446</v>
+        <v>0.001076287846519512</v>
       </c>
       <c r="AE11">
-        <v>-0.000233204434635718</v>
+        <v>-0.0001914444853041382</v>
       </c>
       <c r="AF11">
-        <v>0.0009763827511841003</v>
+        <v>0.001099297044563579</v>
       </c>
       <c r="AG11">
-        <v>-0.6953418085515138</v>
+        <v>-0.6960896475081119</v>
       </c>
       <c r="AH11">
-        <v>-0.01276371984923516</v>
+        <v>-0.01274372732075227</v>
       </c>
       <c r="AI11">
-        <v>-0.7850399449377466</v>
+        <v>-0.7783268934622217</v>
       </c>
       <c r="AJ11">
-        <v>0.08317903240568485</v>
+        <v>0.1965477998387496</v>
       </c>
       <c r="AK11">
-        <v>-0.01155084507233862</v>
+        <v>-0.01144236647475951</v>
       </c>
       <c r="AL11">
-        <v>-3.261066686940718E-05</v>
+        <v>-0.000156522862680149</v>
       </c>
       <c r="AM11">
-        <v>0.5205238680507988</v>
+        <v>0.5168143503470466</v>
       </c>
       <c r="AN11">
-        <v>-0.003008362664594737</v>
+        <v>-0.001136846104067556</v>
       </c>
     </row>
   </sheetData>
